--- a/output/pdf_financials_xlsx/GSY.xlsx
+++ b/output/pdf_financials_xlsx/GSY.xlsx
@@ -909,43 +909,43 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>24.701</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>37.581</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>64.23699999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>100.814</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>138.782</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>172.315</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>255.997</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>535.638</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>698.15</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>888.928</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1133.406</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1278.177</v>
       </c>
     </row>
     <row r="13">
@@ -1657,43 +1657,43 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>15.066</v>
+        <v>-9.635</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>19.327</v>
+        <v>-18.254</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.793</v>
+        <v>-38.444</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>32.718</v>
+        <v>-68.096</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>41.468</v>
+        <v>-97.31399999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>50.553</v>
+        <v>-121.762</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>73.917</v>
+        <v>-182.08</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>31.049</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>319.969</v>
+        <v>-215.669</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>199.353</v>
+        <v>-498.797</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>340.777</v>
+        <v>-548.151</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>365.223</v>
+        <v>-768.183</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-180.92</v>
+        <v>-1459.097</v>
       </c>
     </row>
     <row r="28">
@@ -1749,43 +1749,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>67.83199999999999</v>
+        <v>43.131</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>73.039</v>
+        <v>35.458</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>82.434</v>
+        <v>18.197</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>88.81399999999999</v>
+        <v>-12</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>95.80500000000001</v>
+        <v>-42.977</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>102.761</v>
+        <v>-69.554</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>125.92</v>
+        <v>-130.077</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>31.049</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>398.855</v>
+        <v>-136.783</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>280.659</v>
+        <v>-417.491</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>427.108</v>
+        <v>-461.82</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>449.118</v>
+        <v>-684.288</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-98.744</v>
+        <v>-1376.921</v>
       </c>
     </row>
     <row r="30">
@@ -1795,43 +1795,43 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>33.9715434735793</v>
+        <v>21.60081733634492</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>33.37949125741497</v>
+        <v>16.20463041670094</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>31.809376808798</v>
+        <v>7.021802045147598</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>29.18891916141097</v>
+        <v>-3.943826760836486</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>27.56938749082747</v>
+        <v>-12.36730406756737</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>25.57974549944241</v>
+        <v>-17.31370479528437</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>41.38388881037752</v>
+        <v>-42.75009613077729</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>8.934835469993239</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>48.24535938320258</v>
+        <v>-16.54522318264181</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>27.53351201174097</v>
+        <v>-40.95715249927404</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>34.16675399517947</v>
+        <v>-36.94356071544851</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>29.26092256492883</v>
+        <v>-44.5827114034842</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-5.8194625259829</v>
+        <v>-81.14862837983981</v>
       </c>
     </row>
     <row r="31">
@@ -1946,19 +1946,19 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.165</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.389</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>24.928</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>109.37</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>100.188</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>102.479</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>62.654</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>144.577</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>247.544</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>152.661</v>
       </c>
     </row>
     <row r="35">
@@ -2042,19 +2042,19 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.165</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.389</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>24.928</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>109.37</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>100.188</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2062,19 +2062,19 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>102.479</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>62.654</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>144.577</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>247.544</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>152.661</v>
       </c>
     </row>
     <row r="37">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E334" s="5" t="n">
@@ -42215,7 +42215,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -43256,7 +43256,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSY.xlsx
+++ b/output/pdf_financials_xlsx/GSY.xlsx
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.631</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.329</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.165</v>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.631</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.329</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.165</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>5.536</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>7.206</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>16.508</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>66.584</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
+        <v>103.936</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>180.693</v>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>72.12</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>111.142</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>197.201</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>13.729</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>15.793</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>16.915</v>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>0</v>
+        <v>6.213</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>9.523999999999999</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>11.006</v>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0</v>
+        <v>19.963</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>19.963</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>19.963</v>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>0</v>
+        <v>21.281</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0</v>
+        <v>23.496</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>21.281</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>23.496</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -4243,15 +4243,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.2026511003399579</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.1732321780097764</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -4668,10 +4664,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>60.885</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>79.923</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>80.364</v>
@@ -4860,10 +4856,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.035</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.169</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>6.458</v>
@@ -18313,7 +18309,11 @@
           <t>Cash Note 6</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="n">
         <v>4.631</v>
       </c>
@@ -18388,7 +18388,11 @@
           <t>Amounts receivable Note 7</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>5.536</v>
       </c>
@@ -18463,7 +18467,11 @@
           <t>Consumer loans receivable Note 8</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
         <v>66.584</v>
       </c>
@@ -18613,7 +18621,11 @@
           <t>Property and equipment Note 10</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>13.729</v>
       </c>
@@ -18688,7 +18700,11 @@
           <t>Deferred tax assets Note 18</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>4.232</v>
       </c>
@@ -18763,7 +18779,11 @@
           <t>Intangible assets Note 11</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>6.213</v>
       </c>
@@ -18838,7 +18858,11 @@
           <t>Goodwill Note 11</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
         <v>19.963</v>
       </c>
@@ -18913,7 +18937,11 @@
           <t>Bank revolving credit facility Note 13</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>21.281</v>
       </c>
@@ -18988,7 +19016,11 @@
           <t>Dividends payable Note 15</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DividendsPayable</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
         <v>1.012</v>
       </c>
@@ -19217,7 +19249,11 @@
           <t>Share capital Note 15</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>60.885</v>
       </c>
@@ -19296,7 +19332,11 @@
           <t>Contributed surplus Note 16</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>3.035</v>
       </c>

--- a/output/pdf_financials_xlsx/GSY.xlsx
+++ b/output/pdf_financials_xlsx/GSY.xlsx
@@ -1703,43 +1703,43 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>52.766</v>
+        <v>4.64</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>53.712</v>
+        <v>5.698</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>56.641</v>
+        <v>6.922</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>56.096</v>
+        <v>8.683</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>54.337</v>
+        <v>10.107</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>52.208</v>
+        <v>10.987</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>52.003</v>
+        <v>11.915</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>78.886</v>
+        <v>43.042</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>81.306</v>
+        <v>47.759</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>86.331</v>
+        <v>52.796</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>83.895</v>
+        <v>54.413</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>82.176</v>
+        <v>54.409</v>
       </c>
     </row>
     <row r="29">
@@ -1749,43 +1749,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>43.131</v>
+        <v>-4.995</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35.458</v>
+        <v>-12.556</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.197</v>
+        <v>-31.522</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-12</v>
+        <v>-59.413</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-42.977</v>
+        <v>-87.20699999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-69.554</v>
+        <v>-110.775</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-130.077</v>
+        <v>-170.165</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>31.049</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-136.783</v>
+        <v>-172.627</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-417.491</v>
+        <v>-451.038</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-461.82</v>
+        <v>-495.355</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-684.288</v>
+        <v>-713.77</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1376.921</v>
+        <v>-1404.688</v>
       </c>
     </row>
     <row r="30">
@@ -1795,43 +1795,43 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>21.60081733634492</v>
+        <v>-2.501590099813194</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>16.20463041670094</v>
+        <v>-5.738206878901716</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>7.021802045147598</v>
+        <v>-12.1636118078333</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3.943826760836486</v>
+        <v>-19.52621494513151</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-12.36730406756737</v>
+        <v>-25.09517848664048</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-17.31370479528437</v>
+        <v>-27.57462760873029</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-42.75009613077729</v>
+        <v>-55.92510672981172</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>8.934835469993239</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-16.54522318264181</v>
+        <v>-20.88090071390383</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-40.95715249927404</v>
+        <v>-44.2482164860262</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-36.94356071544851</v>
+        <v>-39.62621263306266</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-44.5827114034842</v>
+        <v>-46.50352178975069</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-81.14862837983981</v>
+        <v>-82.78507227474954</v>
       </c>
     </row>
     <row r="31">
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>5.698</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>6.922</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.683</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>10.107</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>10.987</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>11.915</v>
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
@@ -5225,19 +5225,19 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>43.042</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>47.759</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>52.796</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>54.413</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>54.409</v>
       </c>
     </row>
     <row r="101">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>9.727</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.776</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>170.177</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>60.564</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -20227,7 +20227,11 @@
           <t>Depreciation of right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -20385,7 +20389,11 @@
           <t>Depreciation of property and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -23548,7 +23556,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -23629,7 +23637,11 @@
           <t>Depreciation of right-of-use assets (note 10)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -23791,7 +23803,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -26445,7 +26461,11 @@
           <t>Depreciation of right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -26526,7 +26546,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -26690,7 +26710,11 @@
           <t>Depreciation of property and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -27164,7 +27188,11 @@
           <t>Issuance of common shares, net of issuance costs (note 17)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -27788,7 +27816,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n">
         <v>4.019</v>
       </c>
@@ -27859,7 +27891,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
@@ -32447,7 +32479,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E328" s="5" t="n">
         <v>9.727</v>
       </c>
@@ -34022,7 +34058,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -34099,7 +34135,11 @@
           <t>Depreciation of right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -34174,7 +34214,11 @@
           <t>Depreciation of property and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -35649,7 +35693,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -35730,7 +35774,11 @@
           <t>Depreciation of right-of-use assets (note 10)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -35809,7 +35857,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -41098,7 +41150,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E439" s="5" t="n">
         <v>4.019</v>
       </c>
@@ -41169,7 +41225,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">

--- a/output/pdf_financials_xlsx/GSY.xlsx
+++ b/output/pdf_financials_xlsx/GSY.xlsx
@@ -5186,7 +5186,7 @@
         <v>247.898</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>283.11</v>
+        <v>264.227</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-178.37</v>
@@ -5967,25 +5967,25 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-2.846</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-4.54</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-5.446</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-4.293</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-4.757</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-6.136</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-5.622</v>
       </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
@@ -19747,7 +19747,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -21033,7 +21037,11 @@
           <t>Deferred income tax recovery (note 20)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -24362,7 +24370,11 @@
           <t>Deferred income tax recovery (note 19)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -26793,7 +26805,11 @@
           <t>Deferred income tax recovery (note 21)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -28126,7 +28142,11 @@
           <t>Deferred income tax (recovery) (note 18)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -28363,7 +28383,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E276" s="5" t="n">
         <v>-2.846</v>
       </c>
@@ -29530,7 +29554,11 @@
           <t>Deferred income tax expense (recovery) (note 22)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -31047,7 +31075,11 @@
           <t>Deferred tax expense (recovery) (note 16)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -32157,7 +32189,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E324" s="5" t="n">
         <v>-1.299</v>
       </c>
